--- a/pedidos.xlsx
+++ b/pedidos.xlsx
@@ -417,10 +417,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8.4" customWidth="1" min="1" max="1"/>
+    <col width="10.8" customWidth="1" min="1" max="1"/>
     <col width="14.4" customWidth="1" min="2" max="2"/>
     <col width="7.199999999999999" customWidth="1" min="3" max="3"/>
     <col width="9.6" customWidth="1" min="4" max="4"/>
@@ -457,11 +457,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>cxvcx</t>
+          <t>sdfsdfs</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -470,12 +470,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Efectivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>rggdfg</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>175</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
         </is>
       </c>
     </row>

--- a/pedidos.xlsx
+++ b/pedidos.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Pedidos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="En el local" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Para llevar" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,14 +28,20 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A5276"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -51,7 +58,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,90 +426,220 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.8" customWidth="1" min="1" max="1"/>
-    <col width="14.4" customWidth="1" min="2" max="2"/>
-    <col width="7.199999999999999" customWidth="1" min="3" max="3"/>
-    <col width="9.6" customWidth="1" min="4" max="4"/>
-    <col width="19.2" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="51" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>Mesa/Cliente</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Platillos</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Total (Bs)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Metodo de Pago</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Efectivo recibido (Bs)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Monto QR (Bs)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cambio (Bs)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cambio dado en</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Pagado</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Método de Pago</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sdfsdfs</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>105</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Mesa</t>
-        </is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Quesadilla (Carne) x3; Porc totopos (Normal) x2</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>145</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Mesa/Cliente</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Platillos</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Total (Bs)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Metodo de Pago</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Efectivo recibido (Bs)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Monto QR (Bs)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cambio (Bs)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cambio dado en</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Costo Moto (Bs)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Pago Moto (metodo)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Quesadilla (Carne) x4</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>140</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mixto</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2" t="n">
+        <v>90</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>50</v>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>Efectivo</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>rggdfg</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>175</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Mesa</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Efectivo</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
     </row>
